--- a/results/Int All Data -0.3/Rando_10_permute.xlsx
+++ b/results/Int All Data -0.3/Rando_10_permute.xlsx
@@ -440,1447 +440,1447 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8058407509225956</v>
+        <v>0.7927667108285988</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8042524408844762</v>
+        <v>0.7803778925312672</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8004460409909248</v>
+        <v>0.7794027297166546</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8074290609607151</v>
+        <v>0.7787618615034715</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8074290609607151</v>
+        <v>0.7765437716480394</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8074290609607151</v>
+        <v>0.777814419678535</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8064760749378435</v>
+        <v>0.7625943643022648</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.801711144823485</v>
+        <v>0.7629175705078239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7994930549680531</v>
+        <v>0.7670360882110638</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8004404967929895</v>
+        <v>0.7644615269624613</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8023464688387328</v>
+        <v>0.7577961690002948</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7944104628460709</v>
+        <v>0.7577961690002948</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7953523604730721</v>
+        <v>0.7553103149186564</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7870986924727863</v>
+        <v>0.756580962949152</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7861124412623031</v>
+        <v>0.7359883744329518</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7870876040769157</v>
+        <v>0.7366181542502643</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7813752321376211</v>
+        <v>0.7363004922426404</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7667627797869221</v>
+        <v>0.735971741839146</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7600918776268204</v>
+        <v>0.735971741839146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7511862530174811</v>
+        <v>0.7537386374743427</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7492691925758672</v>
+        <v>0.757545037367894</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7498934281952445</v>
+        <v>0.7505564732001686</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7521170622486117</v>
+        <v>0.7483328391468014</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7549704761192915</v>
+        <v>0.7550037413069031</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7502055460049331</v>
+        <v>0.7534265196646541</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7502000018069979</v>
+        <v>0.7584924791928305</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7714556353281221</v>
+        <v>0.7594454652157021</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7670083672213877</v>
+        <v>0.7623044232843172</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7660387486047102</v>
+        <v>0.7638982775203719</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7536499303073785</v>
+        <v>0.7680389720153529</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7714999889116041</v>
+        <v>0.7565920513450224</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.771817650919228</v>
+        <v>0.7562799335353338</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.719202185810303</v>
+        <v>0.7511973414133516</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7179259935818723</v>
+        <v>0.7556501537180214</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7239172181432441</v>
+        <v>0.7619923054746285</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7210748926684347</v>
+        <v>0.7540507552840313</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7270827498236123</v>
+        <v>0.7686687518326655</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.725795469199311</v>
+        <v>0.7686687518326655</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7255277049731045</v>
+        <v>0.7635861597106832</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7359883744329518</v>
+        <v>0.757545037367894</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7289998102652262</v>
+        <v>0.7664340293834278</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7483383833447366</v>
+        <v>0.7664340293834278</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7454738810781864</v>
+        <v>0.7664118525916866</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.746103660895499</v>
+        <v>0.7765160506583633</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7419740547963883</v>
+        <v>0.7717511205440049</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7441866004538851</v>
+        <v>0.7676215144448943</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7410377013673224</v>
+        <v>0.7644448943686555</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7173294789521713</v>
+        <v>0.75425753333295</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7777368009074415</v>
+        <v>0.7517217814698942</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7780378303212596</v>
+        <v>0.7494648822289154</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7846422021061381</v>
+        <v>0.7317478843751359</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7843245400985143</v>
+        <v>0.7308059867481349</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.783700304479137</v>
+        <v>0.7308004425501996</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7829651849010546</v>
+        <v>0.7345957540478805</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7746211670084904</v>
+        <v>0.7383910655455614</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7672927640414</v>
+        <v>0.7298197355376517</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7657765285764389</v>
+        <v>0.7324164735779953</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7691765592954023</v>
+        <v>0.7368526532888593</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7688699856836489</v>
+        <v>0.7368526532888593</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7570555052242771</v>
+        <v>0.725538793368975</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7606440386730393</v>
+        <v>0.6716898468897872</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7360099352027</v>
+        <v>0.6716787584939166</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7196522925463803</v>
+        <v>0.6754962467833385</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7360859112484794</v>
+        <v>0.6675436081968709</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7351717346111546</v>
+        <v>0.6316184376203809</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7109312691942186</v>
+        <v>0.6615008431287674</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.710234959001683</v>
+        <v>0.6608655191135198</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7435473749660161</v>
+        <v>0.6551642355700955</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7149561515545521</v>
+        <v>0.6551642355700955</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7181105948390498</v>
+        <v>0.6629267287014502</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6546708019538575</v>
+        <v>0.6641530231484638</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6676228696932786</v>
+        <v>0.6639756088145354</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6638830001749503</v>
+        <v>0.6459464931510674</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6734294929974727</v>
+        <v>0.6490787596438243</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6734128604036669</v>
+        <v>0.6458744185779092</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6730397564166904</v>
+        <v>0.6392755909909659</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7112717240155764</v>
+        <v>0.6360934267167917</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7119070480308241</v>
+        <v>0.5670909552365566</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7150393145235809</v>
+        <v>0.5702636738401743</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7172684927748834</v>
+        <v>0.5715842196520872</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7109778815250076</v>
+        <v>0.5322257531690224</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6851070112337772</v>
+        <v>0.5322257531690224</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6693902367906404</v>
+        <v>0.5322257531690224</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6694068693844462</v>
+        <v>0.5296733687121609</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6617497160138612</v>
+        <v>0.5284304416713416</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6617497160138612</v>
+        <v>0.5290325004989778</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6617497160138612</v>
+        <v>0.5270877190676877</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6617497160138612</v>
+        <v>0.5206884826064136</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6673789249841271</v>
+        <v>0.5348929230572104</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6673789249841271</v>
+        <v>0.5333212456128967</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.694686769243911</v>
+        <v>0.5206036769120707</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6331578765804045</v>
+        <v>0.5106175497273486</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6167542376152885</v>
+        <v>0.5099766815141656</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6129589261176076</v>
+        <v>0.5211741132774095</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6132765881252316</v>
+        <v>0.4908592603300728</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.604110386212935</v>
+        <v>0.4954451333851887</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6017243276941311</v>
+        <v>0.4936960416069468</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6014066656865072</v>
+        <v>0.4865006993903025</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6014066656865072</v>
+        <v>0.4802544417239088</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5927854378971802</v>
+        <v>0.4751108634246388</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5747008802543596</v>
+        <v>0.4969747159933272</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5748300395321847</v>
+        <v>0.4969747159933272</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5789042036519426</v>
+        <v>0.4960328183663261</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5714909949905091</v>
+        <v>0.4940492275494892</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5510164773562636</v>
+        <v>0.4969636275974567</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5481353424959076</v>
+        <v>0.4985796586252524</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5427051086293182</v>
+        <v>0.4993829513038722</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5630243887213766</v>
+        <v>0.5004024677019669</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5515830122489813</v>
+        <v>0.5004080118999021</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5257675839371033</v>
+        <v>0.5064713110344323</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5331569730814817</v>
+        <v>0.5061536490268085</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5360896484485691</v>
+        <v>0.505824898623314</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5452963024717267</v>
+        <v>0.5087392986712816</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5452963024717267</v>
+        <v>0.5087392986712816</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5367027956720759</v>
+        <v>0.5090569606789055</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5367027956720759</v>
+        <v>0.5090569606789055</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5405979027325915</v>
+        <v>0.5086450473063823</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5412443151437097</v>
+        <v>0.495197903225409</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5399902997070199</v>
+        <v>0.4973882720911647</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5514593971690914</v>
+        <v>0.4983578907078421</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5272189317521555</v>
+        <v>0.4997560552908486</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5345933310280422</v>
+        <v>0.4935818721976133</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4977389939457358</v>
+        <v>0.4775601668680374</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4991377745507352</v>
+        <v>0.4710239681836961</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4981570675381872</v>
+        <v>0.4710239681836961</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5102848978512331</v>
+        <v>0.4778667404797908</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5017135678433234</v>
+        <v>0.4808144057153699</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5083495620904994</v>
+        <v>0.4808144057153699</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5083495620904994</v>
+        <v>0.4866265732174993</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5070567372682628</v>
+        <v>0.4930796089328117</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.505824898623314</v>
+        <v>0.4930796089328117</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5055072366156902</v>
+        <v>0.4930962415266175</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5030213825340516</v>
+        <v>0.5009529860228716</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5030213825340516</v>
+        <v>0.5009529860228716</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5084050040698519</v>
+        <v>0.501259559634625</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5064380458468208</v>
+        <v>0.5003065736117533</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5091639431649896</v>
+        <v>0.5002954852158829</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5048569227319508</v>
+        <v>0.5009086324393897</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5029953042696895</v>
+        <v>0.5015550448505079</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5029953042696895</v>
+        <v>0.501237382842884</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5029953042696895</v>
+        <v>0.5015716774443136</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5010616112342698</v>
+        <v>0.5015716774443136</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5037027028580956</v>
+        <v>0.5018837952540023</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5043380268733434</v>
+        <v>0.5018893394519376</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5141245629323961</v>
+        <v>0.5018893394519376</v>
       </c>
     </row>
     <row r="147">
@@ -1890,97 +1890,97 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5110311058251861</v>
+        <v>0.5018893394519376</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4993036898074644</v>
+        <v>0.5025357518630559</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5005798820358952</v>
+        <v>0.5025357518630559</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4999112928330359</v>
+        <v>0.502858958068615</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5033889423230928</v>
+        <v>0.5002954852158829</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4999334696247769</v>
+        <v>0.5009308092311306</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4999334696247769</v>
+        <v>0.5025135750713148</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4999334696247769</v>
+        <v>0.5006297798173125</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4989915719977758</v>
+        <v>0.4996379844088941</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4980441301728393</v>
+        <v>0.5006020588276362</v>
       </c>
     </row>
   </sheetData>
